--- a/Collections/EURO/Croatia/#EURO#Croatia#Regular#[2008-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Croatia/#EURO#Croatia#Regular#[2008-present]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Croatia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1E002A-9CE0-4245-8464-967EDD5A8B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3E2CE1-15BE-42A1-BF23-157758ADE907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -396,7 +399,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="52">
   <si>
     <t>Year</t>
   </si>
@@ -461,12 +464,6 @@
     <t>High convenience set of tables table of actual coins with photos</t>
   </si>
   <si>
-    <t>40.000.000</t>
-  </si>
-  <si>
-    <t>30.000.000</t>
-  </si>
-  <si>
     <t>Obv: Without mint symbol</t>
   </si>
   <si>
@@ -488,21 +485,9 @@
     <t>Obv: Geographical map of Croatia</t>
   </si>
   <si>
-    <t>72.000.000</t>
-  </si>
-  <si>
     <t>63.000.000</t>
   </si>
   <si>
-    <t>80.000.000</t>
-  </si>
-  <si>
-    <t>50.000.000</t>
-  </si>
-  <si>
-    <t>45.000.000</t>
-  </si>
-  <si>
     <t>Subject</t>
   </si>
   <si>
@@ -513,6 +498,63 @@
   </si>
   <si>
     <t>Subtype_2#Map_of_Europe</t>
+  </si>
+  <si>
+    <t>93.006.050</t>
+  </si>
+  <si>
+    <t>1.089.506</t>
+  </si>
+  <si>
+    <t>9.600.000</t>
+  </si>
+  <si>
+    <t>69.313.000</t>
+  </si>
+  <si>
+    <t>6.420.000</t>
+  </si>
+  <si>
+    <t>95.464.500</t>
+  </si>
+  <si>
+    <t>13.080.806</t>
+  </si>
+  <si>
+    <t>8.700.000</t>
+  </si>
+  <si>
+    <t>102.879.740</t>
+  </si>
+  <si>
+    <t>1.048.006</t>
+  </si>
+  <si>
+    <t>21.040.000</t>
+  </si>
+  <si>
+    <t>89.180.020</t>
+  </si>
+  <si>
+    <t>4.500.806</t>
+  </si>
+  <si>
+    <t>14.500.000</t>
+  </si>
+  <si>
+    <t>65.039.479</t>
+  </si>
+  <si>
+    <t>1.028.006</t>
+  </si>
+  <si>
+    <t>48.061.650</t>
+  </si>
+  <si>
+    <t>79.368.450</t>
+  </si>
+  <si>
+    <t>1.008.006</t>
   </si>
 </sst>
 </file>
@@ -793,7 +835,143 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="28">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -898,9 +1076,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="18" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1169,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -1200,19 +1378,19 @@
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26"/>
       <c r="B2" s="24" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -1221,20 +1399,64 @@
         <v>2023</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="str">
         <f t="shared" ref="G3" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f t="shared" ref="G4:G5" si="1">IF(OR(AND(F4&gt;1,F4&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1246,11 +1468,45 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="16" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1270,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -1301,19 +1557,19 @@
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26"/>
       <c r="B2" s="24" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -1322,20 +1578,64 @@
         <v>2023</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="str">
         <f t="shared" ref="G3" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f t="shared" ref="G4:G5" si="1">IF(OR(AND(F4&gt;1,F4&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1347,11 +1647,45 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="26" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1371,7 +1705,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -1402,19 +1736,19 @@
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26"/>
       <c r="B2" s="24" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -1423,20 +1757,64 @@
         <v>2023</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="10" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="str">
         <f t="shared" ref="G3" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="9"/>
+      <c r="E4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f t="shared" ref="G4:G5" si="1">IF(OR(AND(F4&gt;1,F4&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1448,11 +1826,45 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1472,7 +1884,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -1503,19 +1915,19 @@
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26"/>
       <c r="B2" s="24" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -1524,22 +1936,70 @@
         <v>2023</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="str">
         <f t="shared" ref="G3" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f t="shared" ref="G4:G5" si="1">IF(OR(AND(F4&gt;1,F4&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1550,11 +2010,45 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1574,7 +2068,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -1605,19 +2099,19 @@
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26"/>
       <c r="B2" s="24" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -1626,22 +2120,70 @@
         <v>2023</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="str">
         <f t="shared" ref="G3" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f t="shared" ref="G4:G5" si="1">IF(OR(AND(F4&gt;1,F4&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1652,11 +2194,45 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3">
+    <cfRule type="containsText" dxfId="23" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1676,7 +2252,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -1707,19 +2283,19 @@
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26"/>
       <c r="B2" s="24" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -1728,22 +2304,68 @@
         <v>2023</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="str">
         <f t="shared" ref="G3" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f t="shared" ref="G4:G5" si="1">IF(OR(AND(F4&gt;1,F4&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1754,11 +2376,45 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="22" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1778,7 +2434,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -1809,19 +2465,19 @@
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26"/>
       <c r="B2" s="24" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -1830,22 +2486,68 @@
         <v>2023</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="str">
         <f t="shared" ref="G3" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f t="shared" ref="G4:G5" si="1">IF(OR(AND(F4&gt;1,F4&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1857,11 +2559,45 @@
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="21" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -1912,19 +2648,19 @@
     <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26"/>
       <c r="B2" s="24" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2"/>
     </row>
@@ -1933,22 +2669,68 @@
         <v>2023</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="3" t="str">
         <f t="shared" ref="G3" si="0">IF(OR(AND(F3&gt;1,F3&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f t="shared" ref="G4:G5" si="1">IF(OR(AND(F4&gt;1,F4&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -1963,11 +2745,45 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="20" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F5))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
